--- a/serverFireStation/fire_station_project/report_templates/driver.xlsx
+++ b/serverFireStation/fire_station_project/report_templates/driver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Дмитрий\Desktop\Diplom_Application\FFGSM\serverFireStation\fire_station_project\report_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E319F5D-C6F7-41C8-AF69-209847CC3E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E198CA2C-7425-4FD0-9921-55050BF685A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="4185" windowWidth="24315" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -211,21 +211,71 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,56 +283,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,9 +567,10 @@
   <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" customWidth="1"/>
@@ -581,207 +582,207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="12"/>
+      <c r="J4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="9" t="s">
+    <row r="5" spans="1:19" ht="57" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="8"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="18"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="2">
         <v>5</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="9">
         <v>6</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="3">
         <v>7</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="3">
         <v>8</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="3">
         <v>9</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="4">
         <v>10</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="3">
         <v>11</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="3">
         <v>12</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="4">
         <v>13</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="5">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
